--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -11690,10 +11690,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117926330</v>
+        <v>117926371</v>
       </c>
       <c r="B89" t="n">
-        <v>8416</v>
+        <v>96801</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11706,21 +11706,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11730,10 +11730,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>534641</v>
+        <v>534618</v>
       </c>
       <c r="R89" t="n">
-        <v>6722005</v>
+        <v>6722000</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11802,10 +11802,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117926371</v>
+        <v>117926330</v>
       </c>
       <c r="B90" t="n">
-        <v>96801</v>
+        <v>8416</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11818,21 +11818,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11842,10 +11842,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>534618</v>
+        <v>534641</v>
       </c>
       <c r="R90" t="n">
-        <v>6722000</v>
+        <v>6722005</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -11690,10 +11690,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117926371</v>
+        <v>117550675</v>
       </c>
       <c r="B89" t="n">
-        <v>96801</v>
+        <v>8416</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11706,21 +11706,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11730,13 +11730,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>534618</v>
+        <v>534684</v>
       </c>
       <c r="R89" t="n">
-        <v>6722000</v>
+        <v>6722125</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11760,22 +11760,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11802,10 +11802,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117926330</v>
+        <v>117926371</v>
       </c>
       <c r="B90" t="n">
-        <v>8416</v>
+        <v>96808</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11818,21 +11818,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11842,10 +11842,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>534641</v>
+        <v>534618</v>
       </c>
       <c r="R90" t="n">
-        <v>6722005</v>
+        <v>6722000</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11914,7 +11914,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117550675</v>
+        <v>117926330</v>
       </c>
       <c r="B91" t="n">
         <v>8416</v>
@@ -11954,13 +11954,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>534684</v>
+        <v>534641</v>
       </c>
       <c r="R91" t="n">
-        <v>6722125</v>
+        <v>6722005</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11984,22 +11984,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -11802,10 +11802,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117926371</v>
+        <v>117926330</v>
       </c>
       <c r="B90" t="n">
-        <v>96808</v>
+        <v>8416</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11818,21 +11818,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11842,10 +11842,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>534618</v>
+        <v>534641</v>
       </c>
       <c r="R90" t="n">
-        <v>6722000</v>
+        <v>6722005</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11914,10 +11914,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117926330</v>
+        <v>117926371</v>
       </c>
       <c r="B91" t="n">
-        <v>8416</v>
+        <v>96808</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11930,21 +11930,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11954,10 +11954,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>534641</v>
+        <v>534618</v>
       </c>
       <c r="R91" t="n">
-        <v>6722005</v>
+        <v>6722000</v>
       </c>
       <c r="S91" t="n">
         <v>1</v>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -11690,10 +11690,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117550675</v>
+        <v>117926371</v>
       </c>
       <c r="B89" t="n">
-        <v>8416</v>
+        <v>96808</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11706,21 +11706,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -11730,13 +11730,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>534684</v>
+        <v>534618</v>
       </c>
       <c r="R89" t="n">
-        <v>6722125</v>
+        <v>6722000</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11760,22 +11760,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11914,10 +11914,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117926371</v>
+        <v>117550675</v>
       </c>
       <c r="B91" t="n">
-        <v>96808</v>
+        <v>8416</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11930,21 +11930,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11954,13 +11954,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>534618</v>
+        <v>534684</v>
       </c>
       <c r="R91" t="n">
-        <v>6722000</v>
+        <v>6722125</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11984,22 +11984,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12409,6 +12409,455 @@
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>124909133</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>534692</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6722096</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>124909406</v>
+      </c>
+      <c r="B96" t="n">
+        <v>8447</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>534692</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6722096</v>
+      </c>
+      <c r="S96" t="n">
+        <v>15</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>124909058</v>
+      </c>
+      <c r="B97" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>534692</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6722096</v>
+      </c>
+      <c r="S97" t="n">
+        <v>15</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Evalena Sköld, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>124906888</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>534778</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6721985</v>
+      </c>
+      <c r="S98" t="n">
+        <v>15</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Åke Sköld, Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -12853,7 +12853,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -12853,7 +12853,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12858,6 +12858,119 @@
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>126116245</v>
+      </c>
+      <c r="B99" t="n">
+        <v>58508</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>534715</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6722003</v>
+      </c>
+      <c r="S99" t="n">
+        <v>50</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -12414,7 +12414,7 @@
         <v>124909133</v>
       </c>
       <c r="B95" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>124906888</v>
       </c>
       <c r="B98" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>126116245</v>
       </c>
       <c r="B99" t="n">
-        <v>58508</v>
+        <v>58509</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -12414,7 +12414,7 @@
         <v>124909133</v>
       </c>
       <c r="B95" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>124906888</v>
       </c>
       <c r="B98" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>126116245</v>
       </c>
       <c r="B99" t="n">
-        <v>58509</v>
+        <v>58513</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -12414,7 +12414,7 @@
         <v>124909133</v>
       </c>
       <c r="B95" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>124906888</v>
       </c>
       <c r="B98" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>126116245</v>
       </c>
       <c r="B99" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -12519,7 +12519,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld</t>
+          <t>Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AY101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13078,6 +13078,122 @@
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127348881</v>
+      </c>
+      <c r="B101" t="n">
+        <v>92627</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>534696</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6722040</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -13083,7 +13083,7 @@
         <v>127348881</v>
       </c>
       <c r="B101" t="n">
-        <v>92627</v>
+        <v>92628</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -12976,7 +12976,7 @@
         <v>124908561</v>
       </c>
       <c r="B100" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>127348881</v>
       </c>
       <c r="B101" t="n">
-        <v>92628</v>
+        <v>92632</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -12976,7 +12976,7 @@
         <v>124908561</v>
       </c>
       <c r="B100" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>127348881</v>
       </c>
       <c r="B101" t="n">
-        <v>92632</v>
+        <v>92634</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -13083,7 +13083,7 @@
         <v>127348881</v>
       </c>
       <c r="B101" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -12976,7 +12976,7 @@
         <v>124908561</v>
       </c>
       <c r="B100" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>127348881</v>
       </c>
       <c r="B101" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -12976,7 +12976,7 @@
         <v>124908561</v>
       </c>
       <c r="B100" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>127348881</v>
       </c>
       <c r="B101" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -13083,7 +13083,7 @@
         <v>127348881</v>
       </c>
       <c r="B101" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -13083,7 +13083,7 @@
         <v>127348881</v>
       </c>
       <c r="B101" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 43185-2023 artfynd.xlsx
+++ b/artfynd/A 43185-2023 artfynd.xlsx
@@ -13083,7 +13083,7 @@
         <v>127348881</v>
       </c>
       <c r="B101" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
